--- a/Results/2_parametrization/diagnostics/pam_parametrizer_diagnostics_iML1515.xlsx
+++ b/Results/2_parametrization/diagnostics/pam_parametrizer_diagnostics_iML1515.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="125">
   <si>
     <t>run_id</t>
   </si>
@@ -38,214 +38,247 @@
     <t>ga_error</t>
   </si>
   <si>
+    <t>P00509</t>
+  </si>
+  <si>
     <t>P06959_P0A9P0_P0AFG8</t>
   </si>
   <si>
+    <t>P09373</t>
+  </si>
+  <si>
     <t>P0A6P9</t>
   </si>
   <si>
+    <t>P0A9B2</t>
+  </si>
+  <si>
+    <t>P0AB71</t>
+  </si>
+  <si>
+    <t>P26458_P26459</t>
+  </si>
+  <si>
+    <t>P42632</t>
+  </si>
+  <si>
+    <t>P77399</t>
+  </si>
+  <si>
+    <t>P77733</t>
+  </si>
+  <si>
+    <t>P0A6A3</t>
+  </si>
+  <si>
+    <t>P0A754</t>
+  </si>
+  <si>
     <t>P0A799</t>
   </si>
   <si>
-    <t>P0A9B2</t>
-  </si>
-  <si>
-    <t>P0AB71</t>
-  </si>
-  <si>
     <t>P0AB80</t>
   </si>
   <si>
     <t>P0AEP1</t>
   </si>
   <si>
-    <t>P26458_P26459</t>
-  </si>
-  <si>
-    <t>P37339</t>
-  </si>
-  <si>
-    <t>P77399</t>
+    <t>P15640</t>
+  </si>
+  <si>
+    <t>P60844</t>
   </si>
   <si>
     <t>P00944</t>
   </si>
   <si>
-    <t>P06149</t>
-  </si>
-  <si>
-    <t>P06999</t>
+    <t>P07001_P0AB67</t>
   </si>
   <si>
     <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
   </si>
   <si>
-    <t>P0A991</t>
+    <t>P0A796</t>
+  </si>
+  <si>
+    <t>P0A825</t>
+  </si>
+  <si>
+    <t>P0A867</t>
+  </si>
+  <si>
+    <t>P0AB89</t>
+  </si>
+  <si>
+    <t>P05793</t>
+  </si>
+  <si>
+    <t>P07014_P0AC41_P0AC44_P69054</t>
+  </si>
+  <si>
+    <t>P0A9G6</t>
   </si>
   <si>
     <t>P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
   </si>
   <si>
-    <t>P15640</t>
-  </si>
-  <si>
-    <t>P07001_P0AB67</t>
-  </si>
-  <si>
-    <t>P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
-  </si>
-  <si>
-    <t>P07003</t>
-  </si>
-  <si>
-    <t>P09053</t>
-  </si>
-  <si>
-    <t>P0A6A8_P0AAI9</t>
-  </si>
-  <si>
-    <t>P0AB89</t>
-  </si>
-  <si>
-    <t>P33570</t>
-  </si>
-  <si>
-    <t>P07014_P0AC41_P0AC44_P69054</t>
-  </si>
-  <si>
-    <t>P08200</t>
-  </si>
-  <si>
-    <t>P0A825</t>
-  </si>
-  <si>
-    <t>P0A9P0_P0AFG3_P0AFG6</t>
-  </si>
-  <si>
     <t>P25516</t>
   </si>
   <si>
-    <t>P33221</t>
-  </si>
-  <si>
     <t>P33940</t>
   </si>
   <si>
+    <t>b</t>
+  </si>
+  <si>
     <t>f</t>
   </si>
   <si>
-    <t>b</t>
+    <t>CE_ASPTA_P00509</t>
+  </si>
+  <si>
+    <t>CE_CYSTA_P00509</t>
+  </si>
+  <si>
+    <t>CE_PHETA1_P00509</t>
+  </si>
+  <si>
+    <t>CE_TYRTA_P00509</t>
   </si>
   <si>
     <t>CE_PDH_P06959_P0A9P0_P0AFG8</t>
   </si>
   <si>
+    <t>CE_PFL_P09373</t>
+  </si>
+  <si>
+    <t>CE_OBTFL_P09373</t>
+  </si>
+  <si>
     <t>CE_ENO_P0A6P9</t>
   </si>
   <si>
+    <t>CE_NADHHS_P0A9B2</t>
+  </si>
+  <si>
+    <t>CE_GAPD_P0A9B2</t>
+  </si>
+  <si>
+    <t>CE_NADHHR_P0A9B2</t>
+  </si>
+  <si>
+    <t>CE_NADPHHS_P0A9B2</t>
+  </si>
+  <si>
+    <t>CE_NADPHHR_P0A9B2</t>
+  </si>
+  <si>
+    <t>CE_FBA_P0AB71</t>
+  </si>
+  <si>
+    <t>CE_FBA3_P0AB71</t>
+  </si>
+  <si>
+    <t>CE_CYTBDpp_P26458_P26459</t>
+  </si>
+  <si>
+    <t>CE_CYTBD2pp_P26458_P26459</t>
+  </si>
+  <si>
+    <t>CE_OBTFL_P42632</t>
+  </si>
+  <si>
+    <t>CE_PFL_P42632</t>
+  </si>
+  <si>
+    <t>CE_ECOAH5_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD3_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD8_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD7_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD6_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD2_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD5_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD4_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH3_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH6_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH4_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH7_P77399</t>
+  </si>
+  <si>
+    <t>CE_HACD1_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH2_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH1_P77399</t>
+  </si>
+  <si>
+    <t>CE_ECOAH8_P77399</t>
+  </si>
+  <si>
+    <t>CE_FORt2pp_P77733</t>
+  </si>
+  <si>
+    <t>CE_FORtppi_P77733</t>
+  </si>
+  <si>
+    <t>CE_ACKr_P0A6A3</t>
+  </si>
+  <si>
+    <t>CE_NADH10_P0A754</t>
+  </si>
+  <si>
+    <t>CE_NADH5_P0A754</t>
+  </si>
+  <si>
+    <t>CE_NADH9_P0A754</t>
+  </si>
+  <si>
     <t>CE_PGK_P0A799</t>
   </si>
   <si>
-    <t>CE_NADPHHS_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_GAPD_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_NADHHR_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_NADHHS_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_NADPHHR_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_E4PD_P0A9B2</t>
-  </si>
-  <si>
-    <t>CE_FBA_P0AB71</t>
-  </si>
-  <si>
-    <t>CE_FBA3_P0AB71</t>
-  </si>
-  <si>
     <t>CE_ILETA_P0AB80</t>
   </si>
   <si>
+    <t>CE_LEUTAi_P0AB80</t>
+  </si>
+  <si>
     <t>CE_VALTA_P0AB80</t>
   </si>
   <si>
-    <t>CE_PHETA1_P0AB80</t>
-  </si>
-  <si>
-    <t>CE_LEUTAi_P0AB80</t>
-  </si>
-  <si>
-    <t>CE_TYRTA_P0AB80</t>
-  </si>
-  <si>
     <t>CE_GLCt2pp_P0AEP1</t>
   </si>
   <si>
     <t>CE_GALt2pp_P0AEP1</t>
   </si>
   <si>
-    <t>CE_CYTBD2pp_P26458_P26459</t>
-  </si>
-  <si>
-    <t>CE_CYTBDpp_P26458_P26459</t>
-  </si>
-  <si>
-    <t>CE_SHGO_P37339</t>
-  </si>
-  <si>
-    <t>CE_HACD6_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD8_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD3_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD5_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD4_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD2_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH1_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH2_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH3_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH4_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH5_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH6_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH7_P77399</t>
-  </si>
-  <si>
-    <t>CE_ECOAH8_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD1_P77399</t>
-  </si>
-  <si>
-    <t>CE_HACD7_P77399</t>
+    <t>CE_PRAGSr_P15640</t>
+  </si>
+  <si>
+    <t>CE_H2Otpp_P60844</t>
   </si>
   <si>
     <t>CE_XYLI2_P00944</t>
@@ -254,94 +287,70 @@
     <t>CE_XYLI1_P00944</t>
   </si>
   <si>
-    <t>CE_LDH_D2_P06149</t>
-  </si>
-  <si>
-    <t>CE_PFK_P06999</t>
+    <t>CE_THD2pp_P07001_P0AB67</t>
   </si>
   <si>
     <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P68699</t>
   </si>
   <si>
-    <t>CE_FBA_P0A991</t>
+    <t>CE_PFK_P0A796</t>
+  </si>
+  <si>
+    <t>CE_PFK_3_P0A796</t>
+  </si>
+  <si>
+    <t>CE_PFK_2_P0A796</t>
+  </si>
+  <si>
+    <t>CE_ALATA_D2_P0A825</t>
+  </si>
+  <si>
+    <t>CE_ALATA_L2_P0A825</t>
+  </si>
+  <si>
+    <t>CE_GHMT2r_P0A825</t>
+  </si>
+  <si>
+    <t>CE_THFAT_P0A825</t>
+  </si>
+  <si>
+    <t>CE_THRA2_P0A825</t>
+  </si>
+  <si>
+    <t>CE_TALA_P0A867</t>
+  </si>
+  <si>
+    <t>CE_ADSL2r_P0AB89</t>
+  </si>
+  <si>
+    <t>CE_ADSL1r_P0AB89</t>
+  </si>
+  <si>
+    <t>CE_KARA1_P05793</t>
+  </si>
+  <si>
+    <t>CE_KARA2_P05793</t>
+  </si>
+  <si>
+    <t>CE_SUCDi_P07014_P0AC41_P0AC44_P69054</t>
+  </si>
+  <si>
+    <t>CE_ICL_P0A9G6</t>
   </si>
   <si>
     <t>CE_CYTBO3_4pp_P0ABI8_P0ABJ1_P0ABJ3_P0ABJ6</t>
   </si>
   <si>
-    <t>CE_PRAGSr_P15640</t>
-  </si>
-  <si>
-    <t>CE_THD2pp_P07001_P0AB67</t>
-  </si>
-  <si>
-    <t>CE_ATPS4rpp_P0A6E6_P0AB98_P0ABA0_P0ABA4_P0ABA6_P0ABB0_P0ABB4_P0ABC0_P68699</t>
-  </si>
-  <si>
-    <t>CE_POX_P07003</t>
-  </si>
-  <si>
-    <t>CE_VPAMTr_P09053</t>
-  </si>
-  <si>
-    <t>CE_MCOATA_P0A6A8_P0AAI9</t>
-  </si>
-  <si>
-    <t>CE_ADSL1r_P0AB89</t>
-  </si>
-  <si>
-    <t>CE_ADSL2r_P0AB89</t>
-  </si>
-  <si>
-    <t>CE_TKT2_P33570</t>
-  </si>
-  <si>
-    <t>CE_TKT1_P33570</t>
-  </si>
-  <si>
-    <t>CE_SUCDi_P07014_P0AC41_P0AC44_P69054</t>
-  </si>
-  <si>
-    <t>CE_ICDHyr_P08200</t>
-  </si>
-  <si>
-    <t>CE_THRA2_P0A825</t>
-  </si>
-  <si>
-    <t>CE_THRA_P0A825</t>
-  </si>
-  <si>
-    <t>CE_ALATA_D2_P0A825</t>
-  </si>
-  <si>
-    <t>CE_GHMT2r_P0A825</t>
-  </si>
-  <si>
-    <t>CE_THFAT_P0A825</t>
-  </si>
-  <si>
-    <t>CE_ALATA_L2_P0A825</t>
-  </si>
-  <si>
-    <t>CE_AKGDH_P0A9P0_P0AFG3_P0AFG6</t>
+    <t>CE_ACONTb_P25516</t>
   </si>
   <si>
     <t>CE_ACONTa_P25516</t>
   </si>
   <si>
-    <t>CE_ACONTb_P25516</t>
-  </si>
-  <si>
-    <t>CE_ACKr_P33221</t>
-  </si>
-  <si>
-    <t>CE_GART_P33221</t>
+    <t>CE_MDH2_P33940</t>
   </si>
   <si>
     <t>CE_MDH3_P33940</t>
-  </si>
-  <si>
-    <t>CE_MDH2_P33940</t>
   </si>
   <si>
     <t>time_s</t>
@@ -741,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:F310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -772,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>189.7540064432013</v>
+        <v>3.220566563151269</v>
       </c>
       <c r="F2">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -792,16 +801,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
         <v>39</v>
       </c>
       <c r="E3">
-        <v>217.9219576635404</v>
+        <v>8.049549479741282</v>
       </c>
       <c r="F3">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -809,19 +818,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
       </c>
       <c r="E4">
-        <v>41.31897738958594</v>
+        <v>31.81896273030134</v>
       </c>
       <c r="F4">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -829,19 +838,19 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
       </c>
       <c r="E5">
-        <v>33.18327797288364</v>
+        <v>3.935999999999999</v>
       </c>
       <c r="F5">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -849,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -858,10 +867,10 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>205.3547743126631</v>
+        <v>103.9117061806308</v>
       </c>
       <c r="F6">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -869,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>150.9152473191612</v>
+        <v>13.82373322666921</v>
       </c>
       <c r="F7">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -889,19 +898,19 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>32.99999999999999</v>
+        <v>0.284788597234679</v>
       </c>
       <c r="F8">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -909,19 +918,19 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E9">
-        <v>277.4467087526347</v>
+        <v>6.194399999999999</v>
       </c>
       <c r="F9">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -929,19 +938,19 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10">
-        <v>75.12552561958094</v>
+        <v>360.4889238679555</v>
       </c>
       <c r="F10">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -949,19 +958,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E11">
-        <v>58.8115597349067</v>
+        <v>193.9784240899286</v>
       </c>
       <c r="F11">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -969,19 +978,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>41.8901126143456</v>
+        <v>9.350708677287455</v>
       </c>
       <c r="F12">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -989,19 +998,19 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E13">
-        <v>40.21327333419817</v>
+        <v>18.811458272724</v>
       </c>
       <c r="F13">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1009,19 +1018,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E14">
-        <v>32.99999999999999</v>
+        <v>18.2379</v>
       </c>
       <c r="F14">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1029,19 +1038,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E15">
-        <v>438.8460219252435</v>
+        <v>13.47855216502582</v>
       </c>
       <c r="F15">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1049,19 +1058,19 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E16">
-        <v>1.3191</v>
+        <v>35.90669999999999</v>
       </c>
       <c r="F16">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1069,19 +1078,19 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17">
-        <v>7.472779051178792</v>
+        <v>20.48961994647629</v>
       </c>
       <c r="F17">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1095,13 +1104,13 @@
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E18">
-        <v>3.804566586549885</v>
+        <v>41.09999999999997</v>
       </c>
       <c r="F18">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1109,19 +1118,19 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19">
-        <v>0.513</v>
+        <v>31.57653473135981</v>
       </c>
       <c r="F19">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1129,19 +1138,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E20">
-        <v>0.3893859436629652</v>
+        <v>57.93126812256094</v>
       </c>
       <c r="F20">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1149,19 +1158,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E21">
-        <v>0.4186619187644257</v>
+        <v>95.6110098321867</v>
       </c>
       <c r="F21">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1169,19 +1178,19 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E22">
-        <v>91.10080403260496</v>
+        <v>33.02327135434282</v>
       </c>
       <c r="F22">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1189,19 +1198,19 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E23">
-        <v>0.2116864058633367</v>
+        <v>230.4651042765917</v>
       </c>
       <c r="F23">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1215,13 +1224,13 @@
         <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E24">
-        <v>133.7386081542821</v>
+        <v>1.3191</v>
       </c>
       <c r="F24">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1232,16 +1241,16 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25">
-        <v>0.4601495429414962</v>
+        <v>14.34756514528567</v>
       </c>
       <c r="F25">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1255,13 +1264,13 @@
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E26">
-        <v>20.54167375454178</v>
+        <v>4.954675191351363</v>
       </c>
       <c r="F26">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1269,19 +1278,19 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E27">
-        <v>174.4139131969905</v>
+        <v>8.271899999999999</v>
       </c>
       <c r="F27">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1295,13 +1304,13 @@
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E28">
-        <v>34.9760728435005</v>
+        <v>27.22453861514648</v>
       </c>
       <c r="F28">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1309,19 +1318,19 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E29">
-        <v>8.052717033324887</v>
+        <v>1645.704220075202</v>
       </c>
       <c r="F29">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1335,13 +1344,13 @@
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E30">
-        <v>10.24573295114897</v>
+        <v>7.4162435704915</v>
       </c>
       <c r="F30">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1349,19 +1358,19 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E31">
-        <v>36.57716302110716</v>
+        <v>6.17068371788332</v>
       </c>
       <c r="F31">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1369,19 +1378,19 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
         <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E32">
-        <v>5.922900000000001</v>
+        <v>9.793477694669562</v>
       </c>
       <c r="F32">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1389,19 +1398,19 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E33">
-        <v>1.189194853185834</v>
+        <v>11.4522</v>
       </c>
       <c r="F33">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1409,19 +1418,19 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E34">
-        <v>45.66886722909391</v>
+        <v>1.0242</v>
       </c>
       <c r="F34">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1429,19 +1438,19 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E35">
-        <v>2.639222803267336</v>
+        <v>2.618399999999999</v>
       </c>
       <c r="F35">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1449,19 +1458,19 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
         <v>37</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E36">
-        <v>6.361834108127277</v>
+        <v>4.575288504112027</v>
       </c>
       <c r="F36">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1469,19 +1478,19 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E37">
-        <v>2.456985694605598</v>
+        <v>41.09999999999997</v>
       </c>
       <c r="F37">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1489,19 +1498,19 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E38">
-        <v>24.39601526490894</v>
+        <v>589.5712149581221</v>
       </c>
       <c r="F38">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1509,19 +1518,19 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E39">
-        <v>15.6585157744706</v>
+        <v>1.5231</v>
       </c>
       <c r="F39">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1529,19 +1538,19 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E40">
-        <v>2.7666</v>
+        <v>6.363987514771793</v>
       </c>
       <c r="F40">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1549,19 +1558,19 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
         <v>37</v>
       </c>
       <c r="D41" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E41">
-        <v>5.76959306275949</v>
+        <v>2.664850584859731</v>
       </c>
       <c r="F41">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1569,19 +1578,19 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E42">
-        <v>1.0158</v>
+        <v>2.367076064533275</v>
       </c>
       <c r="F42">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1589,19 +1598,19 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E43">
-        <v>6.89890956128435</v>
+        <v>0.9799522028442266</v>
       </c>
       <c r="F43">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1609,19 +1618,19 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E44">
-        <v>0.8727438561576585</v>
+        <v>15.14422665658857</v>
       </c>
       <c r="F44">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1629,19 +1638,19 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E45">
-        <v>2.035353114742577</v>
+        <v>27.22453861514648</v>
       </c>
       <c r="F45">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1649,19 +1658,19 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E46">
-        <v>2.673623097873697</v>
+        <v>38.1152726781413</v>
       </c>
       <c r="F46">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1669,19 +1678,19 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E47">
-        <v>5.440392996811143</v>
+        <v>32.23990837320365</v>
       </c>
       <c r="F47">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1689,19 +1698,19 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E48">
-        <v>0.1980416838687216</v>
+        <v>12.3168244123443</v>
       </c>
       <c r="F48">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1709,19 +1718,19 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E49">
-        <v>2.756683113276627</v>
+        <v>7.570969913317164</v>
       </c>
       <c r="F49">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1729,19 +1738,19 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E50">
-        <v>1.055200513868435</v>
+        <v>2.879752196223149</v>
       </c>
       <c r="F50">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1749,19 +1758,19 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
         <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E51">
-        <v>1.197405508893958</v>
+        <v>0.8279942948861798</v>
       </c>
       <c r="F51">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1769,19 +1778,19 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E52">
-        <v>1.594461265614436</v>
+        <v>1.02</v>
       </c>
       <c r="F52">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1789,19 +1798,19 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E53">
-        <v>3.131519356546534</v>
+        <v>0.8385290803644337</v>
       </c>
       <c r="F53">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1809,19 +1818,19 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E54">
-        <v>0.2595734810067556</v>
+        <v>0.558865730286306</v>
       </c>
       <c r="F54">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1829,19 +1838,19 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
         <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E55">
-        <v>76.20417292750302</v>
+        <v>10.20419200420517</v>
       </c>
       <c r="F55">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1849,19 +1858,19 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E56">
-        <v>3.936823045186216</v>
+        <v>5.20812334919326</v>
       </c>
       <c r="F56">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1869,19 +1878,19 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E57">
-        <v>3.332593322045062</v>
+        <v>1.475816276234234</v>
       </c>
       <c r="F57">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1889,19 +1898,19 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
         <v>37</v>
       </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E58">
-        <v>5.739300000000001</v>
+        <v>1.433485980506492</v>
       </c>
       <c r="F58">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1909,19 +1918,19 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E59">
-        <v>3.646375772268016</v>
+        <v>2.504868264370379</v>
       </c>
       <c r="F59">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1929,159 +1938,159 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E60">
-        <v>11.7403444011563</v>
+        <v>5.014219155565327</v>
       </c>
       <c r="F60">
-        <v>-4.000418660250907</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
         <v>37</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E61">
-        <v>66.6735</v>
+        <v>1.451096463643493</v>
       </c>
       <c r="F61">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E62">
-        <v>376.0366852132673</v>
+        <v>1.0158</v>
       </c>
       <c r="F62">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E63">
-        <v>133.8860508619801</v>
+        <v>4.372836915457483</v>
       </c>
       <c r="F63">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E64">
-        <v>57.8153265445449</v>
+        <v>124.0624748295123</v>
       </c>
       <c r="F64">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D65" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E65">
-        <v>309.1136607271476</v>
+        <v>36.59339862339813</v>
       </c>
       <c r="F65">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
         <v>37</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E66">
-        <v>191.2630235320172</v>
+        <v>82.60243008783011</v>
       </c>
       <c r="F66">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E67">
-        <v>32.99999999999999</v>
+        <v>24.59180458608218</v>
       </c>
       <c r="F67">
-        <v>-3.381450617683306</v>
+        <v>-5.574799177032772</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2089,19 +2098,19 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
         <v>37</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E68">
-        <v>26.05204472690086</v>
+        <v>360.4889238679555</v>
       </c>
       <c r="F68">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2112,16 +2121,16 @@
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E69">
-        <v>36.06413815977437</v>
+        <v>425.1620932940083</v>
       </c>
       <c r="F69">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2129,19 +2138,19 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="E70">
-        <v>75.61629927203876</v>
+        <v>28.73122518469039</v>
       </c>
       <c r="F70">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2149,19 +2158,19 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
         <v>37</v>
       </c>
       <c r="D71" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E71">
-        <v>9.643403222013038</v>
+        <v>3.382778272619935</v>
       </c>
       <c r="F71">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2169,19 +2178,19 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D72" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="E72">
-        <v>4.6206</v>
+        <v>13.65913434589712</v>
       </c>
       <c r="F72">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2189,19 +2198,19 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E73">
-        <v>3400.894324137651</v>
+        <v>169.3258882171647</v>
       </c>
       <c r="F73">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2209,19 +2218,19 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
         <v>37</v>
       </c>
       <c r="D74" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E74">
-        <v>0.5353102164951893</v>
+        <v>212.12282686001</v>
       </c>
       <c r="F74">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2229,19 +2238,19 @@
         <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D75" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E75">
-        <v>6.124386598192258</v>
+        <v>35.8731728155274</v>
       </c>
       <c r="F75">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2249,19 +2258,19 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D76" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E76">
-        <v>2.456985694605598</v>
+        <v>67.90314157064451</v>
       </c>
       <c r="F76">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2269,19 +2278,19 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C77" t="s">
         <v>37</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E77">
-        <v>22.96640868842642</v>
+        <v>149.2234590081569</v>
       </c>
       <c r="F77">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2289,19 +2298,19 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E78">
-        <v>12.03961197377635</v>
+        <v>70.09139999999999</v>
       </c>
       <c r="F78">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2309,19 +2318,19 @@
         <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D79" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E79">
-        <v>7.649181852958723</v>
+        <v>17.21129084441501</v>
       </c>
       <c r="F79">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2329,19 +2338,19 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
         <v>37</v>
       </c>
       <c r="D80" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E80">
-        <v>3.491542883380366</v>
+        <v>95.6110098321867</v>
       </c>
       <c r="F80">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2349,19 +2358,19 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E81">
-        <v>1.0158</v>
+        <v>57.93126812256094</v>
       </c>
       <c r="F81">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2369,19 +2378,19 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E82">
-        <v>5.76959306275949</v>
+        <v>23.01258366510265</v>
       </c>
       <c r="F82">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2389,19 +2398,19 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D83" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E83">
-        <v>0.8727438561576585</v>
+        <v>182.2138454445424</v>
       </c>
       <c r="F83">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2409,19 +2418,19 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
         <v>37</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E84">
-        <v>14.05743706553555</v>
+        <v>743.3383503433744</v>
       </c>
       <c r="F84">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2429,19 +2438,19 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D85" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E85">
-        <v>1.408389815822115</v>
+        <v>5.293194626345335</v>
       </c>
       <c r="F85">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2449,19 +2458,19 @@
         <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E86">
-        <v>3.603740379023394</v>
+        <v>14.34756514528567</v>
       </c>
       <c r="F86">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2469,19 +2478,19 @@
         <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
         <v>37</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E87">
-        <v>4.241471755305954</v>
+        <v>2.637368437816772</v>
       </c>
       <c r="F87">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2489,19 +2498,19 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E88">
-        <v>0.1980416838687216</v>
+        <v>35.05503670801286</v>
       </c>
       <c r="F88">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2509,19 +2518,19 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E89">
-        <v>1.959455274428739</v>
+        <v>0.3074005116997506</v>
       </c>
       <c r="F89">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2529,19 +2538,19 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
         <v>37</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E90">
-        <v>1.676863727397393</v>
+        <v>5.083844771480893</v>
       </c>
       <c r="F90">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2549,19 +2558,19 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E91">
-        <v>1.594461265614436</v>
+        <v>0.8678382548087498</v>
       </c>
       <c r="F91">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2569,19 +2578,19 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C92" t="s">
         <v>37</v>
       </c>
       <c r="D92" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E92">
-        <v>0.8913216167658826</v>
+        <v>0.312733610101628</v>
       </c>
       <c r="F92">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2589,19 +2598,19 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E93">
-        <v>0.8450117064009927</v>
+        <v>0.7755</v>
       </c>
       <c r="F93">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2609,19 +2618,19 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
         <v>37</v>
       </c>
       <c r="D94" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E94">
-        <v>3.131519356546535</v>
+        <v>0.4567497200438747</v>
       </c>
       <c r="F94">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2629,19 +2638,19 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
         <v>37</v>
       </c>
       <c r="D95" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E95">
-        <v>76.20417292750304</v>
+        <v>32.70221419932069</v>
       </c>
       <c r="F95">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2649,19 +2658,19 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E96">
-        <v>2.480707200497311</v>
+        <v>41.09999999999997</v>
       </c>
       <c r="F96">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2669,19 +2678,19 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97" t="s">
         <v>37</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E97">
-        <v>7.298673560795013</v>
+        <v>3.670280792460393</v>
       </c>
       <c r="F97">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2689,19 +2698,19 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D98" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E98">
-        <v>5.688176384887165</v>
+        <v>256.5288863600383</v>
       </c>
       <c r="F98">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2709,19 +2718,19 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E99">
-        <v>6.099784432982892</v>
+        <v>21.89048626450066</v>
       </c>
       <c r="F99">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2729,19 +2738,19 @@
         <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E100">
-        <v>2.639222803267336</v>
+        <v>1.5231</v>
       </c>
       <c r="F100">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -2749,19 +2758,19 @@
         <v>2</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E101">
-        <v>11.7403444011563</v>
+        <v>0.8469440214118451</v>
       </c>
       <c r="F101">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2769,19 +2778,19 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E102">
-        <v>34.08992310576819</v>
+        <v>558.5417548327712</v>
       </c>
       <c r="F102">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2789,19 +2798,19 @@
         <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E103">
-        <v>5.440392996811143</v>
+        <v>32.23990837320365</v>
       </c>
       <c r="F103">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2809,499 +2818,499 @@
         <v>2</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D104" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E104">
-        <v>0.2595734810067556</v>
+        <v>38.1152726781413</v>
       </c>
       <c r="F104">
-        <v>-3.381450617683306</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E105">
-        <v>354.871582969405</v>
+        <v>79.97388590077371</v>
       </c>
       <c r="F105">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D106" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="E106">
-        <v>3125.433807461709</v>
+        <v>98.13325561869704</v>
       </c>
       <c r="F106">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="E107">
-        <v>96.31281245138226</v>
+        <v>1.169802485887285</v>
       </c>
       <c r="F107">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C108" t="s">
         <v>37</v>
       </c>
       <c r="D108" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E108">
-        <v>36.77613150804491</v>
+        <v>1.451096463643493</v>
       </c>
       <c r="F108">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E109">
-        <v>140.9123821432347</v>
+        <v>5.014219155565327</v>
       </c>
       <c r="F109">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C110" t="s">
         <v>37</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E110">
-        <v>164.7579621943524</v>
+        <v>1.393874275966436</v>
       </c>
       <c r="F110">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D111" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E111">
-        <v>18.70977851537901</v>
+        <v>12.44017460956208</v>
       </c>
       <c r="F111">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C112" t="s">
         <v>37</v>
       </c>
       <c r="D112" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="E112">
-        <v>45.94575115180671</v>
+        <v>126.0685590464366</v>
       </c>
       <c r="F112">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E113">
-        <v>8.897087577569883</v>
+        <v>17.55780944549951</v>
       </c>
       <c r="F113">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
         <v>37</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E114">
-        <v>82.8281614896281</v>
+        <v>50.15458928431902</v>
       </c>
       <c r="F114">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
       </c>
       <c r="D115" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E115">
-        <v>1.11297187553475</v>
+        <v>1.475816276234234</v>
       </c>
       <c r="F115">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C116" t="s">
         <v>37</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E116">
-        <v>294.0955561391912</v>
+        <v>0.8279942948861798</v>
       </c>
       <c r="F116">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E117">
-        <v>140.6535588948685</v>
+        <v>1.02</v>
       </c>
       <c r="F117">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E118">
-        <v>0.4601495429414962</v>
+        <v>1.433485980506492</v>
       </c>
       <c r="F118">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E119">
-        <v>0.2116864058633367</v>
+        <v>0.558865730286306</v>
       </c>
       <c r="F119">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D120" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E120">
-        <v>0.3893859436629652</v>
+        <v>22.7262871862618</v>
       </c>
       <c r="F120">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E121">
-        <v>0.2580896610311804</v>
+        <v>124.0624748295123</v>
       </c>
       <c r="F121">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C122" t="s">
         <v>37</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E122">
-        <v>768.6757248933632</v>
+        <v>10.88409171056114</v>
       </c>
       <c r="F122">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E123">
-        <v>0.8575108279341506</v>
+        <v>4.716060301496362</v>
       </c>
       <c r="F123">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D124" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="E124">
-        <v>9.649147771505172</v>
+        <v>4.087202389031861</v>
       </c>
       <c r="F124">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E125">
-        <v>46.16249176167238</v>
+        <v>7.315797402824202</v>
       </c>
       <c r="F125">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C126" t="s">
         <v>37</v>
       </c>
       <c r="D126" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E126">
-        <v>5.309818799862002</v>
+        <v>6.363987514771793</v>
       </c>
       <c r="F126">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C127" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E127">
-        <v>0.5034313322524303</v>
+        <v>0.8385290803644337</v>
       </c>
       <c r="F127">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C128" t="s">
         <v>37</v>
       </c>
       <c r="D128" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E128">
-        <v>4.120961304021266</v>
+        <v>18.25567957515047</v>
       </c>
       <c r="F128">
-        <v>-2.394891246663275</v>
+        <v>-5.204247160725902</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3309,19 +3318,19 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D129" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E129">
-        <v>0.9820379263620048</v>
+        <v>257062.7888704863</v>
       </c>
       <c r="F129">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3329,19 +3338,19 @@
         <v>3</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E130">
-        <v>0.443620388804443</v>
+        <v>169.6913757372394</v>
       </c>
       <c r="F130">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3349,19 +3358,19 @@
         <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E131">
-        <v>3.917682464408792</v>
+        <v>70.19782156195296</v>
       </c>
       <c r="F131">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3369,19 +3378,19 @@
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D132" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E132">
-        <v>11.46042595413306</v>
+        <v>1.111828135970942</v>
       </c>
       <c r="F132">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3389,19 +3398,19 @@
         <v>3</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
         <v>37</v>
       </c>
       <c r="D133" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E133">
-        <v>36.23967267058848</v>
+        <v>252.4343223646568</v>
       </c>
       <c r="F133">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3409,19 +3418,19 @@
         <v>3</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D134" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E134">
-        <v>1.556773597417951</v>
+        <v>13986.08988825726</v>
       </c>
       <c r="F134">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3429,19 +3438,19 @@
         <v>3</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C135" t="s">
         <v>37</v>
       </c>
       <c r="D135" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E135">
-        <v>16.14744380638849</v>
+        <v>238.322131097499</v>
       </c>
       <c r="F135">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3449,19 +3458,19 @@
         <v>3</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E136">
-        <v>1.345080648175236</v>
+        <v>146.9627253056879</v>
       </c>
       <c r="F136">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3469,19 +3478,19 @@
         <v>3</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E137">
-        <v>33.0136679475563</v>
+        <v>303.7304017848895</v>
       </c>
       <c r="F137">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3489,19 +3498,19 @@
         <v>3</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>37</v>
       </c>
       <c r="D138" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E138">
-        <v>0.7274121214647454</v>
+        <v>2.11952283950995</v>
       </c>
       <c r="F138">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3509,19 +3518,19 @@
         <v>3</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E139">
-        <v>0.6946043797624412</v>
+        <v>89.11369638048676</v>
       </c>
       <c r="F139">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3529,19 +3538,19 @@
         <v>3</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>37</v>
       </c>
       <c r="D140" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E140">
-        <v>1.572365725013171</v>
+        <v>155.2694963828729</v>
       </c>
       <c r="F140">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3549,19 +3558,19 @@
         <v>3</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C141" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D141" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E141">
-        <v>7.882108143401765</v>
+        <v>0.1863933578660979</v>
       </c>
       <c r="F141">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -3569,19 +3578,19 @@
         <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E142">
-        <v>3.611564109306856</v>
+        <v>2.392244557274107</v>
       </c>
       <c r="F142">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3589,19 +3598,19 @@
         <v>3</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C143" t="s">
         <v>37</v>
       </c>
       <c r="D143" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E143">
-        <v>4.579091584404456</v>
+        <v>4.348641270405547</v>
       </c>
       <c r="F143">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -3609,19 +3618,19 @@
         <v>3</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E144">
-        <v>52.92170102902223</v>
+        <v>0.64241708142109</v>
       </c>
       <c r="F144">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3629,19 +3638,19 @@
         <v>3</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D145" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E145">
-        <v>7.520241958830393</v>
+        <v>0.2484706047756725</v>
       </c>
       <c r="F145">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3649,19 +3658,19 @@
         <v>3</v>
       </c>
       <c r="B146" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E146">
-        <v>1.621063197546008</v>
+        <v>1.835111067286951</v>
       </c>
       <c r="F146">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -3669,19 +3678,19 @@
         <v>3</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D147" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="E147">
-        <v>7.425135013099364</v>
+        <v>7041.507613483544</v>
       </c>
       <c r="F147">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3689,19 +3698,19 @@
         <v>3</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C148" t="s">
         <v>37</v>
       </c>
       <c r="D148" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E148">
-        <v>1.415832369812017</v>
+        <v>107.1006382173465</v>
       </c>
       <c r="F148">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -3709,19 +3718,19 @@
         <v>3</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D149" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E149">
-        <v>5.911625744527183</v>
+        <v>8.191078166720558</v>
       </c>
       <c r="F149">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -3729,19 +3738,19 @@
         <v>3</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D150" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E150">
-        <v>130.8124217006829</v>
+        <v>4.077377556264445</v>
       </c>
       <c r="F150">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -3749,19 +3758,19 @@
         <v>3</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E151">
-        <v>71.49161719904264</v>
+        <v>2424.109647152561</v>
       </c>
       <c r="F151">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -3769,19 +3778,19 @@
         <v>3</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C152" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D152" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E152">
-        <v>0.8368984144815218</v>
+        <v>74.85480142688398</v>
       </c>
       <c r="F152">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -3789,639 +3798,639 @@
         <v>3</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D153" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E153">
-        <v>2.975261351435941</v>
+        <v>30.15777281597155</v>
       </c>
       <c r="F153">
-        <v>-2.394891246663275</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B154" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C154" t="s">
         <v>37</v>
       </c>
       <c r="D154" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E154">
-        <v>109.1285836492689</v>
+        <v>124.8016801473369</v>
       </c>
       <c r="F154">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="E155">
-        <v>24.35059125246266</v>
+        <v>10.63322310397766</v>
       </c>
       <c r="F155">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C156" t="s">
         <v>37</v>
       </c>
       <c r="D156" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E156">
-        <v>3.532613644750052</v>
+        <v>113.4350846308187</v>
       </c>
       <c r="F156">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B157" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E157">
-        <v>72.4870731309274</v>
+        <v>1.5231</v>
       </c>
       <c r="F157">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B158" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C158" t="s">
         <v>37</v>
       </c>
       <c r="D158" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E158">
-        <v>1163.720604757865</v>
+        <v>28.06638848632497</v>
       </c>
       <c r="F158">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B159" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E159">
-        <v>77.03814099906151</v>
+        <v>1112.030794776973</v>
       </c>
       <c r="F159">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D160" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E160">
-        <v>27.19208666500749</v>
+        <v>350.3537367898912</v>
       </c>
       <c r="F160">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C161" t="s">
         <v>37</v>
       </c>
       <c r="D161" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E161">
-        <v>0.07085678527471166</v>
+        <v>27.87223134322569</v>
       </c>
       <c r="F161">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D162" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E162">
-        <v>21.55180406478715</v>
+        <v>6.681614749721193</v>
       </c>
       <c r="F162">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C163" t="s">
         <v>37</v>
       </c>
       <c r="D163" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E163">
-        <v>47.68861548901523</v>
+        <v>65.92616576820528</v>
       </c>
       <c r="F163">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E164">
-        <v>944.8508668747918</v>
+        <v>4.092979780012629</v>
       </c>
       <c r="F164">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
         <v>37</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E165">
-        <v>5616.999681731772</v>
+        <v>3.503981587032504</v>
       </c>
       <c r="F165">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E166">
-        <v>0.164549566728767</v>
+        <v>52.86345412772113</v>
       </c>
       <c r="F166">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C167" t="s">
         <v>37</v>
       </c>
       <c r="D167" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E167">
-        <v>3.696173716423596</v>
+        <v>18.54769052840611</v>
       </c>
       <c r="F167">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B168" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D168" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E168">
-        <v>1.432389165610632</v>
+        <v>1.155695636364936</v>
       </c>
       <c r="F168">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D169" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="E169">
-        <v>1.836888460716671</v>
+        <v>51.85395870947684</v>
       </c>
       <c r="F169">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B170" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D170" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="E170">
-        <v>53.6613</v>
+        <v>8.008604013437683</v>
       </c>
       <c r="F170">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B171" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D171" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="E171">
-        <v>56.18133829539645</v>
+        <v>962.6829108345516</v>
       </c>
       <c r="F171">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B172" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
         <v>37</v>
       </c>
       <c r="D172" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E172">
-        <v>0.7301204860118993</v>
+        <v>8.056946547210069</v>
       </c>
       <c r="F172">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B173" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C173" t="s">
         <v>37</v>
       </c>
       <c r="D173" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E173">
-        <v>2.056769311588872</v>
+        <v>79.29170348010196</v>
       </c>
       <c r="F173">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B174" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E174">
-        <v>9.692598379049102</v>
+        <v>17.18557019290094</v>
       </c>
       <c r="F174">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B175" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="E175">
-        <v>25.15318754125041</v>
+        <v>5.822115600140659</v>
       </c>
       <c r="F175">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D176" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E176">
-        <v>4.360039011168712</v>
+        <v>56.35704384500123</v>
       </c>
       <c r="F176">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D177" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E177">
-        <v>55.60459036190946</v>
+        <v>0.4783640874815269</v>
       </c>
       <c r="F177">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D178" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E178">
-        <v>1.628286071644779</v>
+        <v>1.618033514763332</v>
       </c>
       <c r="F178">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C179" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E179">
-        <v>222.7018638339804</v>
+        <v>4.069862075346308</v>
       </c>
       <c r="F179">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C180" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D180" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E180">
-        <v>11.46042595413306</v>
+        <v>20.63265558244979</v>
       </c>
       <c r="F180">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C181" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E181">
-        <v>2.510824418985151</v>
+        <v>0.467786685039899</v>
       </c>
       <c r="F181">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C182" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D182" t="s">
         <v>67</v>
       </c>
       <c r="E182">
-        <v>0.2689698704112982</v>
+        <v>1.204671353651518</v>
       </c>
       <c r="F182">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C183" t="s">
         <v>37</v>
       </c>
       <c r="D183" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E183">
-        <v>14.71940279329485</v>
+        <v>0.7995197387035933</v>
       </c>
       <c r="F183">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C184" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D184" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E184">
-        <v>13.19412657307274</v>
+        <v>36.06339351981886</v>
       </c>
       <c r="F184">
-        <v>-1.357897708309521</v>
+        <v>-4.408003692858996</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4429,19 +4438,19 @@
         <v>4</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C185" t="s">
         <v>37</v>
       </c>
       <c r="D185" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E185">
-        <v>8.677630275118581</v>
+        <v>51.97432279070273</v>
       </c>
       <c r="F185">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4449,19 +4458,19 @@
         <v>4</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C186" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D186" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E186">
-        <v>1.145770655904116</v>
+        <v>3.604112418007426</v>
       </c>
       <c r="F186">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4469,19 +4478,19 @@
         <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C187" t="s">
         <v>37</v>
       </c>
       <c r="D187" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E187">
-        <v>10.91325593362463</v>
+        <v>24.51696176137599</v>
       </c>
       <c r="F187">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4489,19 +4498,19 @@
         <v>4</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C188" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D188" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E188">
-        <v>0.7704113624529116</v>
+        <v>1.688848559658678</v>
       </c>
       <c r="F188">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4509,19 +4518,19 @@
         <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C189" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D189" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="E189">
-        <v>1.937244979933902</v>
+        <v>0.9201346188826691</v>
       </c>
       <c r="F189">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4529,19 +4538,19 @@
         <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C190" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D190" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="E190">
-        <v>2.657761555470321</v>
+        <v>40.70542210823837</v>
       </c>
       <c r="F190">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4549,19 +4558,19 @@
         <v>4</v>
       </c>
       <c r="B191" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C191" t="s">
         <v>37</v>
       </c>
       <c r="D191" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E191">
-        <v>150.0668827221967</v>
+        <v>98.27099271297757</v>
       </c>
       <c r="F191">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4569,19 +4578,19 @@
         <v>4</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C192" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D192" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E192">
-        <v>51.21680562352257</v>
+        <v>7.077008514302492</v>
       </c>
       <c r="F192">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4589,19 +4598,19 @@
         <v>4</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C193" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D193" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E193">
-        <v>3.147190818126897</v>
+        <v>105.2183949793268</v>
       </c>
       <c r="F193">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4609,19 +4618,19 @@
         <v>4</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C194" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E194">
-        <v>1.415832369812017</v>
+        <v>65.87966630827735</v>
       </c>
       <c r="F194">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4629,19 +4638,19 @@
         <v>4</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C195" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D195" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E195">
-        <v>86.26558573343142</v>
+        <v>74.40524815386257</v>
       </c>
       <c r="F195">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4649,19 +4658,19 @@
         <v>4</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C196" t="s">
         <v>37</v>
       </c>
       <c r="D196" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="E196">
-        <v>6.01461078754859</v>
+        <v>493.5508759586602</v>
       </c>
       <c r="F196">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4669,19 +4678,19 @@
         <v>4</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D197" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E197">
-        <v>0.2921568882058886</v>
+        <v>74.51290991728315</v>
       </c>
       <c r="F197">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4689,19 +4698,19 @@
         <v>4</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D198" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E198">
-        <v>26.94854676960816</v>
+        <v>0.6186946675278162</v>
       </c>
       <c r="F198">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4709,19 +4718,19 @@
         <v>4</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D199" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E199">
-        <v>4.579091584404456</v>
+        <v>57.5323490788214</v>
       </c>
       <c r="F199">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4729,19 +4738,19 @@
         <v>4</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C200" t="s">
         <v>37</v>
       </c>
       <c r="D200" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E200">
-        <v>2.01553172044566</v>
+        <v>548.6155452569836</v>
       </c>
       <c r="F200">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4749,19 +4758,19 @@
         <v>4</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C201" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D201" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E201">
-        <v>16.0313523785399</v>
+        <v>12.73317877427557</v>
       </c>
       <c r="F201">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4769,19 +4778,19 @@
         <v>4</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C202" t="s">
         <v>37</v>
       </c>
       <c r="D202" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E202">
-        <v>16.06473244501074</v>
+        <v>29.66186471055024</v>
       </c>
       <c r="F202">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4789,19 +4798,19 @@
         <v>4</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C203" t="s">
         <v>37</v>
       </c>
       <c r="D203" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E203">
-        <v>1.126286057985142</v>
+        <v>41.09999999999997</v>
       </c>
       <c r="F203">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4809,19 +4818,19 @@
         <v>4</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C204" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D204" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E204">
-        <v>1.100393809215301</v>
+        <v>0.2767946018244998</v>
       </c>
       <c r="F204">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4829,19 +4838,19 @@
         <v>4</v>
       </c>
       <c r="B205" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C205" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D205" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="E205">
-        <v>69.77926917990162</v>
+        <v>0.06824387018813313</v>
       </c>
       <c r="F205">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4849,84 +4858,84 @@
         <v>4</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D206" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E206">
-        <v>0.5283925603600874</v>
+        <v>62.68868007425899</v>
       </c>
       <c r="F206">
-        <v>-1.357897708309521</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B207" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C207" t="s">
         <v>37</v>
       </c>
       <c r="D207" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E207">
-        <v>24.06630128104163</v>
+        <v>41.09999999999997</v>
       </c>
       <c r="F207">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B208" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C208" t="s">
         <v>37</v>
       </c>
       <c r="D208" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E208">
-        <v>181.0959196677305</v>
+        <v>5.317981576188596</v>
       </c>
       <c r="F208">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B209" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D209" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E209">
-        <v>23.69113949870896</v>
+        <v>0.5486012350368332</v>
       </c>
       <c r="F209">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B210" t="s">
         <v>27</v>
@@ -4935,473 +4944,2013 @@
         <v>37</v>
       </c>
       <c r="D210" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E210">
-        <v>4531.38351159474</v>
+        <v>107.6461225416941</v>
       </c>
       <c r="F210">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B211" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D211" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E211">
-        <v>992.8798067700625</v>
+        <v>64.82429999999999</v>
       </c>
       <c r="F211">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B212" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C212" t="s">
         <v>37</v>
       </c>
       <c r="D212" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E212">
-        <v>72.00490663397152</v>
+        <v>105.982960673062</v>
       </c>
       <c r="F212">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B213" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C213" t="s">
         <v>37</v>
       </c>
       <c r="D213" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E213">
-        <v>62.09307951956074</v>
+        <v>41.68808790145364</v>
       </c>
       <c r="F213">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B214" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D214" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E214">
-        <v>15327.10863203053</v>
+        <v>438.9007680608256</v>
       </c>
       <c r="F214">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B215" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C215" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D215" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E215">
-        <v>0.5412740467461169</v>
+        <v>1050.690719616664</v>
       </c>
       <c r="F215">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B216" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C216" t="s">
         <v>37</v>
       </c>
       <c r="D216" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E216">
-        <v>4.050988139864074</v>
+        <v>34.32012227377357</v>
       </c>
       <c r="F216">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B217" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C217" t="s">
         <v>37</v>
       </c>
       <c r="D217" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E217">
-        <v>171.3765900919205</v>
+        <v>1.151374618046104</v>
       </c>
       <c r="F217">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B218" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C218" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D218" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E218">
-        <v>57.79843027776574</v>
+        <v>172.7811170414313</v>
       </c>
       <c r="F218">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B219" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C219" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D219" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E219">
-        <v>1193.645670574954</v>
+        <v>1.618438604648617</v>
       </c>
       <c r="F219">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B220" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C220" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D220" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E220">
-        <v>5472.794021277899</v>
+        <v>59.81659790752025</v>
       </c>
       <c r="F220">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B221" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C221" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D221" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E221">
-        <v>17.70352767136952</v>
+        <v>1228.373599911714</v>
       </c>
       <c r="F221">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B222" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C222" t="s">
         <v>37</v>
       </c>
       <c r="D222" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E222">
-        <v>0.6623546275928104</v>
+        <v>10.94916236293282</v>
       </c>
       <c r="F222">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B223" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C223" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D223" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="E223">
-        <v>1.138094783707344</v>
+        <v>280.1256749869149</v>
       </c>
       <c r="F223">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B224" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C224" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D224" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="E224">
-        <v>50.63072118609625</v>
+        <v>52.85876620351908</v>
       </c>
       <c r="F224">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B225" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C225" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D225" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E225">
-        <v>19.6146</v>
+        <v>695.9925041912836</v>
       </c>
       <c r="F225">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B226" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C226" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D226" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="E226">
-        <v>8.783238479181685</v>
+        <v>66.88152933318445</v>
       </c>
       <c r="F226">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B227" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C227" t="s">
         <v>37</v>
       </c>
       <c r="D227" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E227">
-        <v>312.8868467082776</v>
+        <v>32.21824940022063</v>
       </c>
       <c r="F227">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B228" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C228" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D228" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="E228">
-        <v>189.5685050814276</v>
+        <v>4589.929465889012</v>
       </c>
       <c r="F228">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B229" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C229" t="s">
         <v>37</v>
       </c>
       <c r="D229" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="E229">
-        <v>100.2371959569851</v>
+        <v>30.52811531697042</v>
       </c>
       <c r="F229">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B230" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C230" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D230" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="E230">
-        <v>38.44475126761503</v>
+        <v>213.5816548126671</v>
       </c>
       <c r="F230">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B231" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C231" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D231" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="E231">
-        <v>42.99687286463001</v>
+        <v>71.87303158928408</v>
       </c>
       <c r="F231">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B232" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C232" t="s">
         <v>37</v>
       </c>
       <c r="D232" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="E232">
-        <v>43.69982400696558</v>
+        <v>3.014935358062106</v>
       </c>
       <c r="F232">
-        <v>-1.191290346597302</v>
+        <v>0.08340202185681302</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233">
+        <v>4</v>
+      </c>
+      <c r="B233" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233" t="s">
+        <v>37</v>
+      </c>
+      <c r="D233" t="s">
+        <v>57</v>
+      </c>
+      <c r="E233">
+        <v>293.4782477960687</v>
+      </c>
+      <c r="F233">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234">
+        <v>4</v>
+      </c>
+      <c r="B234" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234" t="s">
+        <v>37</v>
+      </c>
+      <c r="D234" t="s">
+        <v>72</v>
+      </c>
+      <c r="E234">
+        <v>9.232039190697382</v>
+      </c>
+      <c r="F234">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235">
+        <v>4</v>
+      </c>
+      <c r="B235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235" t="s">
+        <v>37</v>
+      </c>
+      <c r="D235" t="s">
+        <v>59</v>
+      </c>
+      <c r="E235">
+        <v>87.49943262370606</v>
+      </c>
+      <c r="F235">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236">
+        <v>4</v>
+      </c>
+      <c r="B236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236" t="s">
+        <v>36</v>
+      </c>
+      <c r="D236" t="s">
+        <v>59</v>
+      </c>
+      <c r="E236">
+        <v>13815.4691640259</v>
+      </c>
+      <c r="F236">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237">
+        <v>4</v>
+      </c>
+      <c r="B237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" t="s">
+        <v>36</v>
+      </c>
+      <c r="D237" t="s">
+        <v>71</v>
+      </c>
+      <c r="E237">
+        <v>89.68175038967604</v>
+      </c>
+      <c r="F237">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238">
+        <v>4</v>
+      </c>
+      <c r="B238" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238" t="s">
+        <v>37</v>
+      </c>
+      <c r="D238" t="s">
+        <v>70</v>
+      </c>
+      <c r="E238">
+        <v>389.4104134926164</v>
+      </c>
+      <c r="F238">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239">
+        <v>4</v>
+      </c>
+      <c r="B239" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239" t="s">
+        <v>36</v>
+      </c>
+      <c r="D239" t="s">
+        <v>70</v>
+      </c>
+      <c r="E239">
+        <v>4.09297978001263</v>
+      </c>
+      <c r="F239">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240">
+        <v>4</v>
+      </c>
+      <c r="B240" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240" t="s">
+        <v>37</v>
+      </c>
+      <c r="D240" t="s">
+        <v>65</v>
+      </c>
+      <c r="E240">
+        <v>78.81681875026995</v>
+      </c>
+      <c r="F240">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241">
+        <v>4</v>
+      </c>
+      <c r="B241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241" t="s">
+        <v>36</v>
+      </c>
+      <c r="D241" t="s">
+        <v>72</v>
+      </c>
+      <c r="E241">
+        <v>55.94125142498114</v>
+      </c>
+      <c r="F241">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242">
+        <v>4</v>
+      </c>
+      <c r="B242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242" t="s">
+        <v>36</v>
+      </c>
+      <c r="D242" t="s">
+        <v>65</v>
+      </c>
+      <c r="E242">
+        <v>174.2728135009756</v>
+      </c>
+      <c r="F242">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243">
+        <v>4</v>
+      </c>
+      <c r="B243" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243" t="s">
+        <v>36</v>
+      </c>
+      <c r="D243" t="s">
+        <v>67</v>
+      </c>
+      <c r="E243">
+        <v>28.52927725755794</v>
+      </c>
+      <c r="F243">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244">
+        <v>4</v>
+      </c>
+      <c r="B244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244" t="s">
+        <v>36</v>
+      </c>
+      <c r="D244" t="s">
+        <v>57</v>
+      </c>
+      <c r="E244">
+        <v>0.467786685039899</v>
+      </c>
+      <c r="F244">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245">
+        <v>4</v>
+      </c>
+      <c r="B245" t="s">
+        <v>14</v>
+      </c>
+      <c r="C245" t="s">
+        <v>37</v>
+      </c>
+      <c r="D245" t="s">
+        <v>66</v>
+      </c>
+      <c r="E245">
+        <v>4.583112946263104</v>
+      </c>
+      <c r="F245">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246">
+        <v>4</v>
+      </c>
+      <c r="B246" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246" t="s">
+        <v>36</v>
+      </c>
+      <c r="D246" t="s">
+        <v>66</v>
+      </c>
+      <c r="E246">
+        <v>6.410895473068761</v>
+      </c>
+      <c r="F246">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247">
+        <v>4</v>
+      </c>
+      <c r="B247" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247" t="s">
+        <v>37</v>
+      </c>
+      <c r="D247" t="s">
+        <v>68</v>
+      </c>
+      <c r="E247">
+        <v>0.5077868325111097</v>
+      </c>
+      <c r="F247">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248">
+        <v>4</v>
+      </c>
+      <c r="B248" t="s">
+        <v>14</v>
+      </c>
+      <c r="C248" t="s">
+        <v>36</v>
+      </c>
+      <c r="D248" t="s">
+        <v>68</v>
+      </c>
+      <c r="E248">
+        <v>0.4783640874815269</v>
+      </c>
+      <c r="F248">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249">
+        <v>4</v>
+      </c>
+      <c r="B249" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249" t="s">
+        <v>37</v>
+      </c>
+      <c r="D249" t="s">
+        <v>67</v>
+      </c>
+      <c r="E249">
+        <v>3.046135969295571</v>
+      </c>
+      <c r="F249">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250">
+        <v>4</v>
+      </c>
+      <c r="B250" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250" t="s">
+        <v>37</v>
+      </c>
+      <c r="D250" t="s">
+        <v>71</v>
+      </c>
+      <c r="E250">
+        <v>65.92616576820528</v>
+      </c>
+      <c r="F250">
+        <v>0.08340202185681302</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251">
         <v>5</v>
       </c>
-      <c r="B233" t="s">
-        <v>36</v>
-      </c>
-      <c r="C233" t="s">
-        <v>37</v>
-      </c>
-      <c r="D233" t="s">
+      <c r="B251" t="s">
+        <v>6</v>
+      </c>
+      <c r="C251" t="s">
+        <v>36</v>
+      </c>
+      <c r="D251" t="s">
+        <v>39</v>
+      </c>
+      <c r="E251">
+        <v>505.0351858442591</v>
+      </c>
+      <c r="F251">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252">
+        <v>5</v>
+      </c>
+      <c r="B252" t="s">
+        <v>6</v>
+      </c>
+      <c r="C252" t="s">
+        <v>37</v>
+      </c>
+      <c r="D252" t="s">
+        <v>41</v>
+      </c>
+      <c r="E252">
+        <v>51.97432279070273</v>
+      </c>
+      <c r="F252">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253">
+        <v>5</v>
+      </c>
+      <c r="B253" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" t="s">
+        <v>36</v>
+      </c>
+      <c r="D253" t="s">
+        <v>41</v>
+      </c>
+      <c r="E253">
+        <v>2.156487306323864</v>
+      </c>
+      <c r="F253">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254">
+        <v>5</v>
+      </c>
+      <c r="B254" t="s">
+        <v>6</v>
+      </c>
+      <c r="C254" t="s">
+        <v>37</v>
+      </c>
+      <c r="D254" t="s">
+        <v>40</v>
+      </c>
+      <c r="E254">
+        <v>329.0707601914195</v>
+      </c>
+      <c r="F254">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255">
+        <v>5</v>
+      </c>
+      <c r="B255" t="s">
+        <v>6</v>
+      </c>
+      <c r="C255" t="s">
+        <v>36</v>
+      </c>
+      <c r="D255" t="s">
+        <v>40</v>
+      </c>
+      <c r="E255">
+        <v>1.688848559658678</v>
+      </c>
+      <c r="F255">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256">
+        <v>5</v>
+      </c>
+      <c r="B256" t="s">
+        <v>6</v>
+      </c>
+      <c r="C256" t="s">
+        <v>37</v>
+      </c>
+      <c r="D256" t="s">
+        <v>39</v>
+      </c>
+      <c r="E256">
+        <v>0.5798571156373251</v>
+      </c>
+      <c r="F256">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257">
+        <v>5</v>
+      </c>
+      <c r="B257" t="s">
+        <v>6</v>
+      </c>
+      <c r="C257" t="s">
+        <v>36</v>
+      </c>
+      <c r="D257" t="s">
+        <v>38</v>
+      </c>
+      <c r="E257">
+        <v>8.856914352894302</v>
+      </c>
+      <c r="F257">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258">
+        <v>5</v>
+      </c>
+      <c r="B258" t="s">
+        <v>6</v>
+      </c>
+      <c r="C258" t="s">
+        <v>37</v>
+      </c>
+      <c r="D258" t="s">
+        <v>38</v>
+      </c>
+      <c r="E258">
+        <v>50.67874239331199</v>
+      </c>
+      <c r="F258">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259">
+        <v>5</v>
+      </c>
+      <c r="B259" t="s">
+        <v>30</v>
+      </c>
+      <c r="C259" t="s">
+        <v>36</v>
+      </c>
+      <c r="D259" t="s">
+        <v>102</v>
+      </c>
+      <c r="E259">
+        <v>8.036473412018687</v>
+      </c>
+      <c r="F259">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260">
+        <v>5</v>
+      </c>
+      <c r="B260" t="s">
+        <v>30</v>
+      </c>
+      <c r="C260" t="s">
+        <v>37</v>
+      </c>
+      <c r="D260" t="s">
+        <v>102</v>
+      </c>
+      <c r="E260">
+        <v>1.073544999467926</v>
+      </c>
+      <c r="F260">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261">
+        <v>5</v>
+      </c>
+      <c r="B261" t="s">
+        <v>30</v>
+      </c>
+      <c r="C261" t="s">
+        <v>36</v>
+      </c>
+      <c r="D261" t="s">
+        <v>103</v>
+      </c>
+      <c r="E261">
+        <v>41.09999999999997</v>
+      </c>
+      <c r="F261">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262">
+        <v>5</v>
+      </c>
+      <c r="B262" t="s">
+        <v>30</v>
+      </c>
+      <c r="C262" t="s">
+        <v>37</v>
+      </c>
+      <c r="D262" t="s">
+        <v>103</v>
+      </c>
+      <c r="E262">
+        <v>122.0646007728269</v>
+      </c>
+      <c r="F262">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263">
+        <v>5</v>
+      </c>
+      <c r="B263" t="s">
+        <v>31</v>
+      </c>
+      <c r="C263" t="s">
+        <v>37</v>
+      </c>
+      <c r="D263" t="s">
+        <v>104</v>
+      </c>
+      <c r="E263">
+        <v>41.09999999999997</v>
+      </c>
+      <c r="F263">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264">
+        <v>5</v>
+      </c>
+      <c r="B264" t="s">
+        <v>25</v>
+      </c>
+      <c r="C264" t="s">
+        <v>36</v>
+      </c>
+      <c r="D264" t="s">
+        <v>90</v>
+      </c>
+      <c r="E264">
+        <v>11.4038424010551</v>
+      </c>
+      <c r="F264">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265">
+        <v>5</v>
+      </c>
+      <c r="B265" t="s">
+        <v>25</v>
+      </c>
+      <c r="C265" t="s">
+        <v>37</v>
+      </c>
+      <c r="D265" t="s">
+        <v>90</v>
+      </c>
+      <c r="E265">
+        <v>16617.73954675952</v>
+      </c>
+      <c r="F265">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266">
+        <v>5</v>
+      </c>
+      <c r="B266" t="s">
+        <v>26</v>
+      </c>
+      <c r="C266" t="s">
+        <v>37</v>
+      </c>
+      <c r="D266" t="s">
+        <v>92</v>
+      </c>
+      <c r="E266">
+        <v>2727.629982376206</v>
+      </c>
+      <c r="F266">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267">
+        <v>5</v>
+      </c>
+      <c r="B267" t="s">
+        <v>26</v>
+      </c>
+      <c r="C267" t="s">
+        <v>36</v>
+      </c>
+      <c r="D267" t="s">
+        <v>93</v>
+      </c>
+      <c r="E267">
+        <v>0.0682438701881331</v>
+      </c>
+      <c r="F267">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268">
+        <v>5</v>
+      </c>
+      <c r="B268" t="s">
+        <v>26</v>
+      </c>
+      <c r="C268" t="s">
+        <v>37</v>
+      </c>
+      <c r="D268" t="s">
+        <v>93</v>
+      </c>
+      <c r="E268">
+        <v>0.1980024178384118</v>
+      </c>
+      <c r="F268">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269">
+        <v>5</v>
+      </c>
+      <c r="B269" t="s">
+        <v>26</v>
+      </c>
+      <c r="C269" t="s">
+        <v>37</v>
+      </c>
+      <c r="D269" t="s">
+        <v>91</v>
+      </c>
+      <c r="E269">
+        <v>71.98396033013498</v>
+      </c>
+      <c r="F269">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270">
+        <v>5</v>
+      </c>
+      <c r="B270" t="s">
+        <v>32</v>
+      </c>
+      <c r="C270" t="s">
+        <v>37</v>
+      </c>
+      <c r="D270" t="s">
+        <v>105</v>
+      </c>
+      <c r="E270">
+        <v>16.28775164657952</v>
+      </c>
+      <c r="F270">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271">
+        <v>5</v>
+      </c>
+      <c r="B271" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" t="s">
+        <v>36</v>
+      </c>
+      <c r="D271" t="s">
+        <v>105</v>
+      </c>
+      <c r="E271">
+        <v>2.1252</v>
+      </c>
+      <c r="F271">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272">
+        <v>5</v>
+      </c>
+      <c r="B272" t="s">
+        <v>33</v>
+      </c>
+      <c r="C272" t="s">
+        <v>37</v>
+      </c>
+      <c r="D272" t="s">
+        <v>106</v>
+      </c>
+      <c r="E272">
+        <v>349.0713296734991</v>
+      </c>
+      <c r="F272">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273">
+        <v>5</v>
+      </c>
+      <c r="B273" t="s">
+        <v>34</v>
+      </c>
+      <c r="C273" t="s">
+        <v>37</v>
+      </c>
+      <c r="D273" t="s">
         <v>107</v>
       </c>
-      <c r="E233">
-        <v>10.8409698144832</v>
-      </c>
-      <c r="F233">
-        <v>-1.191290346597302</v>
+      <c r="E273">
+        <v>207.5006355025203</v>
+      </c>
+      <c r="F273">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274">
+        <v>5</v>
+      </c>
+      <c r="B274" t="s">
+        <v>34</v>
+      </c>
+      <c r="C274" t="s">
+        <v>36</v>
+      </c>
+      <c r="D274" t="s">
+        <v>107</v>
+      </c>
+      <c r="E274">
+        <v>16.6737</v>
+      </c>
+      <c r="F274">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275">
+        <v>5</v>
+      </c>
+      <c r="B275" t="s">
+        <v>34</v>
+      </c>
+      <c r="C275" t="s">
+        <v>37</v>
+      </c>
+      <c r="D275" t="s">
+        <v>108</v>
+      </c>
+      <c r="E275">
+        <v>8.395517983322449</v>
+      </c>
+      <c r="F275">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276">
+        <v>5</v>
+      </c>
+      <c r="B276" t="s">
+        <v>34</v>
+      </c>
+      <c r="C276" t="s">
+        <v>36</v>
+      </c>
+      <c r="D276" t="s">
+        <v>108</v>
+      </c>
+      <c r="E276">
+        <v>219.648270317755</v>
+      </c>
+      <c r="F276">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277">
+        <v>5</v>
+      </c>
+      <c r="B277" t="s">
+        <v>35</v>
+      </c>
+      <c r="C277" t="s">
+        <v>37</v>
+      </c>
+      <c r="D277" t="s">
+        <v>109</v>
+      </c>
+      <c r="E277">
+        <v>81.37873975697535</v>
+      </c>
+      <c r="F277">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278">
+        <v>5</v>
+      </c>
+      <c r="B278" t="s">
+        <v>35</v>
+      </c>
+      <c r="C278" t="s">
+        <v>37</v>
+      </c>
+      <c r="D278" t="s">
+        <v>110</v>
+      </c>
+      <c r="E278">
+        <v>41.09999999999997</v>
+      </c>
+      <c r="F278">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279">
+        <v>5</v>
+      </c>
+      <c r="B279" t="s">
+        <v>14</v>
+      </c>
+      <c r="C279" t="s">
+        <v>36</v>
+      </c>
+      <c r="D279" t="s">
+        <v>68</v>
+      </c>
+      <c r="E279">
+        <v>1.440086072381072</v>
+      </c>
+      <c r="F279">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280">
+        <v>5</v>
+      </c>
+      <c r="B280" t="s">
+        <v>14</v>
+      </c>
+      <c r="C280" t="s">
+        <v>37</v>
+      </c>
+      <c r="D280" t="s">
+        <v>66</v>
+      </c>
+      <c r="E280">
+        <v>4.583112946263103</v>
+      </c>
+      <c r="F280">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281">
+        <v>5</v>
+      </c>
+      <c r="B281" t="s">
+        <v>14</v>
+      </c>
+      <c r="C281" t="s">
+        <v>36</v>
+      </c>
+      <c r="D281" t="s">
+        <v>66</v>
+      </c>
+      <c r="E281">
+        <v>6.410895473068761</v>
+      </c>
+      <c r="F281">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282">
+        <v>5</v>
+      </c>
+      <c r="B282" t="s">
+        <v>14</v>
+      </c>
+      <c r="C282" t="s">
+        <v>37</v>
+      </c>
+      <c r="D282" t="s">
+        <v>57</v>
+      </c>
+      <c r="E282">
+        <v>82.17731071701155</v>
+      </c>
+      <c r="F282">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283">
+        <v>5</v>
+      </c>
+      <c r="B283" t="s">
+        <v>14</v>
+      </c>
+      <c r="C283" t="s">
+        <v>36</v>
+      </c>
+      <c r="D283" t="s">
+        <v>57</v>
+      </c>
+      <c r="E283">
+        <v>1.408778131908193</v>
+      </c>
+      <c r="F283">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284">
+        <v>5</v>
+      </c>
+      <c r="B284" t="s">
+        <v>14</v>
+      </c>
+      <c r="C284" t="s">
+        <v>37</v>
+      </c>
+      <c r="D284" t="s">
+        <v>67</v>
+      </c>
+      <c r="E284">
+        <v>2.853817080427595</v>
+      </c>
+      <c r="F284">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285">
+        <v>5</v>
+      </c>
+      <c r="B285" t="s">
+        <v>14</v>
+      </c>
+      <c r="C285" t="s">
+        <v>36</v>
+      </c>
+      <c r="D285" t="s">
+        <v>65</v>
+      </c>
+      <c r="E285">
+        <v>182.2480616349872</v>
+      </c>
+      <c r="F285">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286">
+        <v>5</v>
+      </c>
+      <c r="B286" t="s">
+        <v>14</v>
+      </c>
+      <c r="C286" t="s">
+        <v>37</v>
+      </c>
+      <c r="D286" t="s">
+        <v>65</v>
+      </c>
+      <c r="E286">
+        <v>366.4585877764216</v>
+      </c>
+      <c r="F286">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287">
+        <v>5</v>
+      </c>
+      <c r="B287" t="s">
+        <v>14</v>
+      </c>
+      <c r="C287" t="s">
+        <v>37</v>
+      </c>
+      <c r="D287" t="s">
+        <v>68</v>
+      </c>
+      <c r="E287">
+        <v>0.1946338894334929</v>
+      </c>
+      <c r="F287">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288">
+        <v>5</v>
+      </c>
+      <c r="B288" t="s">
+        <v>14</v>
+      </c>
+      <c r="C288" t="s">
+        <v>37</v>
+      </c>
+      <c r="D288" t="s">
+        <v>70</v>
+      </c>
+      <c r="E288">
+        <v>211.980966160475</v>
+      </c>
+      <c r="F288">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289">
+        <v>5</v>
+      </c>
+      <c r="B289" t="s">
+        <v>14</v>
+      </c>
+      <c r="C289" t="s">
+        <v>36</v>
+      </c>
+      <c r="D289" t="s">
+        <v>70</v>
+      </c>
+      <c r="E289">
+        <v>18.82436646867038</v>
+      </c>
+      <c r="F289">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290">
+        <v>5</v>
+      </c>
+      <c r="B290" t="s">
+        <v>14</v>
+      </c>
+      <c r="C290" t="s">
+        <v>37</v>
+      </c>
+      <c r="D290" t="s">
+        <v>71</v>
+      </c>
+      <c r="E290">
+        <v>265.0664606771841</v>
+      </c>
+      <c r="F290">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291">
+        <v>5</v>
+      </c>
+      <c r="B291" t="s">
+        <v>14</v>
+      </c>
+      <c r="C291" t="s">
+        <v>36</v>
+      </c>
+      <c r="D291" t="s">
+        <v>71</v>
+      </c>
+      <c r="E291">
+        <v>89.68175038967604</v>
+      </c>
+      <c r="F291">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292">
+        <v>5</v>
+      </c>
+      <c r="B292" t="s">
+        <v>14</v>
+      </c>
+      <c r="C292" t="s">
+        <v>36</v>
+      </c>
+      <c r="D292" t="s">
+        <v>67</v>
+      </c>
+      <c r="E292">
+        <v>106.9851849047361</v>
+      </c>
+      <c r="F292">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293">
+        <v>5</v>
+      </c>
+      <c r="B293" t="s">
+        <v>14</v>
+      </c>
+      <c r="C293" t="s">
+        <v>36</v>
+      </c>
+      <c r="D293" t="s">
+        <v>72</v>
+      </c>
+      <c r="E293">
+        <v>18.82392371775911</v>
+      </c>
+      <c r="F293">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294">
+        <v>5</v>
+      </c>
+      <c r="B294" t="s">
+        <v>14</v>
+      </c>
+      <c r="C294" t="s">
+        <v>36</v>
+      </c>
+      <c r="D294" t="s">
+        <v>59</v>
+      </c>
+      <c r="E294">
+        <v>15319.19803296143</v>
+      </c>
+      <c r="F294">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295">
+        <v>5</v>
+      </c>
+      <c r="B295" t="s">
+        <v>14</v>
+      </c>
+      <c r="C295" t="s">
+        <v>36</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295">
+        <v>2922.941024570282</v>
+      </c>
+      <c r="F295">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296">
+        <v>5</v>
+      </c>
+      <c r="B296" t="s">
+        <v>14</v>
+      </c>
+      <c r="C296" t="s">
+        <v>37</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296">
+        <v>4.529232680626614</v>
+      </c>
+      <c r="F296">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297">
+        <v>5</v>
+      </c>
+      <c r="B297" t="s">
+        <v>14</v>
+      </c>
+      <c r="C297" t="s">
+        <v>36</v>
+      </c>
+      <c r="D297" t="s">
+        <v>62</v>
+      </c>
+      <c r="E297">
+        <v>292.7378869359462</v>
+      </c>
+      <c r="F297">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298">
+        <v>5</v>
+      </c>
+      <c r="B298" t="s">
+        <v>14</v>
+      </c>
+      <c r="C298" t="s">
+        <v>37</v>
+      </c>
+      <c r="D298" t="s">
+        <v>62</v>
+      </c>
+      <c r="E298">
+        <v>30.34881135757463</v>
+      </c>
+      <c r="F298">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299">
+        <v>5</v>
+      </c>
+      <c r="B299" t="s">
+        <v>14</v>
+      </c>
+      <c r="C299" t="s">
+        <v>36</v>
+      </c>
+      <c r="D299" t="s">
+        <v>58</v>
+      </c>
+      <c r="E299">
+        <v>81127.81294851915</v>
+      </c>
+      <c r="F299">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300">
+        <v>5</v>
+      </c>
+      <c r="B300" t="s">
+        <v>14</v>
+      </c>
+      <c r="C300" t="s">
+        <v>37</v>
+      </c>
+      <c r="D300" t="s">
+        <v>58</v>
+      </c>
+      <c r="E300">
+        <v>30.52811531697042</v>
+      </c>
+      <c r="F300">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301">
+        <v>5</v>
+      </c>
+      <c r="B301" t="s">
+        <v>14</v>
+      </c>
+      <c r="C301" t="s">
+        <v>36</v>
+      </c>
+      <c r="D301" t="s">
+        <v>64</v>
+      </c>
+      <c r="E301">
+        <v>409.7675068699962</v>
+      </c>
+      <c r="F301">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302">
+        <v>5</v>
+      </c>
+      <c r="B302" t="s">
+        <v>14</v>
+      </c>
+      <c r="C302" t="s">
+        <v>37</v>
+      </c>
+      <c r="D302" t="s">
+        <v>64</v>
+      </c>
+      <c r="E302">
+        <v>242.1823624735036</v>
+      </c>
+      <c r="F302">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303">
+        <v>5</v>
+      </c>
+      <c r="B303" t="s">
+        <v>14</v>
+      </c>
+      <c r="C303" t="s">
+        <v>36</v>
+      </c>
+      <c r="D303" t="s">
+        <v>63</v>
+      </c>
+      <c r="E303">
+        <v>233.9661341456212</v>
+      </c>
+      <c r="F303">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304">
+        <v>5</v>
+      </c>
+      <c r="B304" t="s">
+        <v>14</v>
+      </c>
+      <c r="C304" t="s">
+        <v>37</v>
+      </c>
+      <c r="D304" t="s">
+        <v>63</v>
+      </c>
+      <c r="E304">
+        <v>38.14816476631116</v>
+      </c>
+      <c r="F304">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305">
+        <v>5</v>
+      </c>
+      <c r="B305" t="s">
+        <v>14</v>
+      </c>
+      <c r="C305" t="s">
+        <v>36</v>
+      </c>
+      <c r="D305" t="s">
+        <v>61</v>
+      </c>
+      <c r="E305">
+        <v>13128.25516700618</v>
+      </c>
+      <c r="F305">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306">
+        <v>5</v>
+      </c>
+      <c r="B306" t="s">
+        <v>14</v>
+      </c>
+      <c r="C306" t="s">
+        <v>37</v>
+      </c>
+      <c r="D306" t="s">
+        <v>61</v>
+      </c>
+      <c r="E306">
+        <v>10.94916236293282</v>
+      </c>
+      <c r="F306">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307">
+        <v>5</v>
+      </c>
+      <c r="B307" t="s">
+        <v>14</v>
+      </c>
+      <c r="C307" t="s">
+        <v>37</v>
+      </c>
+      <c r="D307" t="s">
+        <v>60</v>
+      </c>
+      <c r="E307">
+        <v>318.3054200962463</v>
+      </c>
+      <c r="F307">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308">
+        <v>5</v>
+      </c>
+      <c r="B308" t="s">
+        <v>14</v>
+      </c>
+      <c r="C308" t="s">
+        <v>37</v>
+      </c>
+      <c r="D308" t="s">
+        <v>59</v>
+      </c>
+      <c r="E308">
+        <v>87.49943262370606</v>
+      </c>
+      <c r="F308">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309">
+        <v>5</v>
+      </c>
+      <c r="B309" t="s">
+        <v>14</v>
+      </c>
+      <c r="C309" t="s">
+        <v>37</v>
+      </c>
+      <c r="D309" t="s">
+        <v>72</v>
+      </c>
+      <c r="E309">
+        <v>25.10785057269586</v>
+      </c>
+      <c r="F309">
+        <v>0.5693864824439886</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310">
+        <v>5</v>
+      </c>
+      <c r="B310" t="s">
+        <v>14</v>
+      </c>
+      <c r="C310" t="s">
+        <v>36</v>
+      </c>
+      <c r="D310" t="s">
+        <v>60</v>
+      </c>
+      <c r="E310">
+        <v>4.102981776677773</v>
+      </c>
+      <c r="F310">
+        <v>0.5693864824439886</v>
       </c>
     </row>
   </sheetData>
@@ -5419,10 +6968,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5430,10 +6979,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3195.425263548001</v>
+        <v>3478.883025222</v>
       </c>
       <c r="C2">
-        <v>0.8876181287633336</v>
+        <v>0.9663563958950001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5441,10 +6990,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2828.765937422</v>
+        <v>2957.285204657999</v>
       </c>
       <c r="C3">
-        <v>0.7857683159505556</v>
+        <v>0.8214681124049997</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5452,10 +7001,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2369.504481951</v>
+        <v>2530.62352225</v>
       </c>
       <c r="C4">
-        <v>0.6581956894308334</v>
+        <v>0.7029509784027778</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5463,10 +7012,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2455.693342322</v>
+        <v>3649.446254805001</v>
       </c>
       <c r="C5">
-        <v>0.6821370395338888</v>
+        <v>1.013735070779167</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5474,10 +7023,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3318.379858961001</v>
+        <v>2895.267422928999</v>
       </c>
       <c r="C6">
-        <v>0.9217721830447226</v>
+        <v>0.8042409508136108</v>
       </c>
     </row>
   </sheetData>
@@ -5495,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5503,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-4.831193649693645</v>
+        <v>-6.213035928532711</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5511,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-4.323896658529827</v>
+        <v>-5.736794076610747</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5519,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-6.254654458914199</v>
+        <v>-5.368753834997392</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5527,7 +7076,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-6.699694159704166</v>
+        <v>-1.351580635591867</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5535,7 +7084,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-6.075376413274824</v>
+        <v>-0.3274890735861599</v>
       </c>
     </row>
   </sheetData>
@@ -5550,21 +7099,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>-0.00434025695802594</v>
@@ -5573,21 +7122,21 @@
         <v>0.0461366449096611</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B3">
-        <v>0.008831170610252719</v>
+        <v>0.008942595098117749</v>
       </c>
       <c r="C3">
-        <v>0.114315371517727</v>
+        <v>0.114491388516627</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5602,15 +7151,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -5618,7 +7167,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B3">
         <v>7</v>
